--- a/src/MxDBUnit/resources/mxdbunit/sample/sample2.xlsx
+++ b/src/MxDBUnit/resources/mxdbunit/sample/sample2.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\MxDBUnit\src\MxDBUnit\resources\mxdbunit\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617FE237-0ED2-4560-9323-E6AFD56E3155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103229CA-4BA8-4D85-82B8-4AAE41870638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43824" yWindow="-4704" windowWidth="21864" windowHeight="10680" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47592" yWindow="-11388" windowWidth="26736" windowHeight="18396" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TestBaseEntity" sheetId="1" r:id="rId1"/>
-    <sheet name="TestExtendedEntity1" sheetId="2" r:id="rId2"/>
-    <sheet name="TestExtendedEntity2" sheetId="3" r:id="rId3"/>
-    <sheet name="=TestBaseEntity" sheetId="6" r:id="rId4"/>
-    <sheet name="=TestExtendedEntity1" sheetId="4" r:id="rId5"/>
-    <sheet name="=TestExtendedEntity2" sheetId="5" r:id="rId6"/>
+    <sheet name="#ReadMe" sheetId="7" r:id="rId1"/>
+    <sheet name="TestBaseEntity" sheetId="1" r:id="rId2"/>
+    <sheet name="TestExtendedEntity1" sheetId="2" r:id="rId3"/>
+    <sheet name="TestExtendedEntity2" sheetId="3" r:id="rId4"/>
+    <sheet name="=TestBaseEntity" sheetId="6" r:id="rId5"/>
+    <sheet name="=TestExtendedEntity1" sheetId="4" r:id="rId6"/>
+    <sheet name="=TestExtendedEntity2" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -92,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="30">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1"/>
@@ -207,6 +208,10 @@
   </si>
   <si>
     <t>ExAttr2 of EX1_003</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Please refer to the "#ReadMe" sheet in "sample1.xlsx".</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -282,10 +287,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,6 +551,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EA09C8-1D9D-4285-ADF9-A5B23638E403}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -606,7 +623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05E46B0-CEF4-4BDF-9530-FE16129087BF}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -672,7 +689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4590BEA-4DDD-4B5B-AD6D-AFF8D05FC44D}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -738,7 +755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A9B2D6-A477-4C7D-82D2-5D5FA067A3DB}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -874,7 +891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B38812-2743-4E3F-8BC2-4CFC09CD07CE}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -954,7 +971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE7B7A-A585-4C99-83DD-26582B26405A}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/src/MxDBUnit/resources/mxdbunit/sample/sample2.xlsx
+++ b/src/MxDBUnit/resources/mxdbunit/sample/sample2.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\MxDBUnit\src\MxDBUnit\resources\mxdbunit\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103229CA-4BA8-4D85-82B8-4AAE41870638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B588C8-E058-4367-A394-24D92AD8A488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47592" yWindow="-11388" windowWidth="26736" windowHeight="18396" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40284" yWindow="-4524" windowWidth="21744" windowHeight="10188" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#ReadMe" sheetId="7" r:id="rId1"/>
-    <sheet name="TestBaseEntity" sheetId="1" r:id="rId2"/>
-    <sheet name="TestExtendedEntity1" sheetId="2" r:id="rId3"/>
-    <sheet name="TestExtendedEntity2" sheetId="3" r:id="rId4"/>
-    <sheet name="=TestBaseEntity" sheetId="6" r:id="rId5"/>
-    <sheet name="=TestExtendedEntity1" sheetId="4" r:id="rId6"/>
-    <sheet name="=TestExtendedEntity2" sheetId="5" r:id="rId7"/>
+    <sheet name="#Alias" sheetId="8" r:id="rId2"/>
+    <sheet name="TestBaseEntity" sheetId="1" r:id="rId3"/>
+    <sheet name="TestExtendedEntity1" sheetId="2" r:id="rId4"/>
+    <sheet name="TestExtendedEntity2" sheetId="3" r:id="rId5"/>
+    <sheet name="=TestBaseEntity" sheetId="6" r:id="rId6"/>
+    <sheet name="=TestExtendedEntity1" sheetId="4" r:id="rId7"/>
+    <sheet name="=TestExtendedEntity2" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,6 +32,33 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>suzuki yuta</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{E3415B1F-0645-49E9-85D3-582148DA4C2F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>If an entity name or table name is too long to be used as a sheet name, you can specify a shortened name in the AliasName field and the actual name in the OriginalName field; the conversion will then be performed at runtime.
+For an external database, specify only the table name in the AliasName field.
+For an internal database, match the inclusion or exclusion of the module name to the sheet name.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>suzuki yuta</author>
@@ -93,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="32">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1"/>
@@ -212,6 +240,14 @@
   </si>
   <si>
     <t>Please refer to the "#ReadMe" sheet in "sample1.xlsx".</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AliasName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OriginalName</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -567,6 +603,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57096108-19F8-4546-BF87-5A913A5DD6D9}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -623,7 +683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05E46B0-CEF4-4BDF-9530-FE16129087BF}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -689,7 +749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4590BEA-4DDD-4B5B-AD6D-AFF8D05FC44D}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -755,7 +815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A9B2D6-A477-4C7D-82D2-5D5FA067A3DB}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -891,7 +951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B38812-2743-4E3F-8BC2-4CFC09CD07CE}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -971,7 +1031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE7B7A-A585-4C99-83DD-26582B26405A}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="18"/>
